--- a/resultat_sammendrag.xlsx
+++ b/resultat_sammendrag.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,6 +501,31 @@
       </c>
       <c r="G3" t="n">
         <v>81.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Rute 3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="G4" t="n">
+        <v>80.90000000000001</v>
       </c>
     </row>
   </sheetData>
